--- a/Sistema de Evidencias OPS.xlsx
+++ b/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84284B1F-FC1B-4F2E-9B72-7361116D6811}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6287FBCA-59FA-4D1A-ABB6-27A1E3E14FD6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4994" uniqueCount="1812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5087" uniqueCount="1841">
   <si>
     <t>Id</t>
   </si>
@@ -5478,6 +5478,93 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/LAYOUT%20One_Jos%C3%A9%20de%20Jes%C3%BAs%20Magos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes%201/IMG_20261009_164743174_HDR_Starbucks%20Central%20In.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues%202/IMG_20261009_164825041_Starbucks%20Central%20In.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/LayOut_Distrital_YAZMIN_GARCIA_GALERIAS_ATIZA_Yazm%C3%ADn%20Haydee%20Garcia.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/17915880456834569902165385879709_Starbucks%20City%20Cente.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_8484_Hector%20Ruben%20Estevez.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/152eb147-d292-48e7-a06c-527e448cacc1_Starbucks%20Apto%20Toluc.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/20261009_173554_Starbucks%20Montevideo.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Hector%20Martinez%20Urib.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/image_Hector%20Martinez%20Urib.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/image_Hector%20Martinez%20Urib.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes%201/17915906185148593836796835910326_Starbucks%20Universida.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues%202/17915907460556263773384330842652_Starbucks%20Universida.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/LayOut_%2038607_Cedros_DT_Christmas_2026-10-09_Erika%20Julieta%20Contre.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38801@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Antenas PB</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17915917171148610501125289418934_Starbucks%20Antenas%20PB.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/IMG_5727_Starbucks%20Patio%20Clav.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/IMG_5910_Julian%20Alejandro%20Flo.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG-20261009-WA0027_Starbucks%20Patio%20Loma.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/17915941445359197407637446512802_Starbucks%20Arboledas.jpg</t>
+  </si>
+  <si>
+    <t>sbmx43111@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Montevideo Insurgentes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/MVIMG_20261009_185938_Starbucks%20Montevideo.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes%201/41863b73-2bed-4fc9-a702-d18f48c751f0_Johan%20Arellano%20Navar.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues%202/608c9d1e-f1d0-4b97-9ef0-4ac5589fd8f0_Johan%20Arellano%20Navar.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/dbeb0f9d-80da-4157-a92d-012919976aa7_Starbucks%20Las%20Am%C3%A9ric.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/IMG_5640_Berenice%20Ivon%20Sanche.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Tarta_Copete_POS/IMG-20261009-WA0046_Starbucks%20Av%20Stim.jpeg</t>
   </si>
 </sst>
 </file>
@@ -5620,8 +5707,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AC1203" totalsRowShown="0">
-  <autoFilter ref="A1:AC1203" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AC1225" totalsRowShown="0">
+  <autoFilter ref="A1:AC1225" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="29">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="26">
       <extLst>
@@ -5830,7 +5917,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="2028" latestEventMarker="2491">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="2050" latestEventMarker="2513">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -6163,7 +6250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC1203"/>
+  <dimension ref="A1:AC1225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="29" width="20" bestFit="1" customWidth="1"/>
@@ -57897,7 +57984,7 @@
       </c>
     </row>
     <row r="1177" spans="1:29">
-      <c r="A1177" s="5">
+      <c r="A1177">
         <v>2002</v>
       </c>
       <c r="B1177" s="3">
@@ -57912,7 +57999,7 @@
       <c r="E1177" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F1177" s="5">
+      <c r="F1177">
         <v>38674</v>
       </c>
       <c r="G1177" s="2" t="s">
@@ -57930,12 +58017,8 @@
       <c r="Q1177" s="4"/>
       <c r="R1177" s="4"/>
       <c r="S1177" s="2"/>
-      <c r="T1177" s="5"/>
-      <c r="U1177" s="5"/>
       <c r="V1177" s="2"/>
       <c r="W1177" s="2"/>
-      <c r="X1177" s="5"/>
-      <c r="Y1177" s="5"/>
       <c r="Z1177" s="2"/>
       <c r="AA1177" s="2"/>
       <c r="AB1177" s="2"/>
@@ -57944,7 +58027,7 @@
       </c>
     </row>
     <row r="1178" spans="1:29">
-      <c r="A1178" s="5">
+      <c r="A1178">
         <v>2003</v>
       </c>
       <c r="B1178" s="3">
@@ -57959,7 +58042,7 @@
       <c r="E1178" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="F1178" s="5">
+      <c r="F1178">
         <v>38106</v>
       </c>
       <c r="G1178" s="2" t="s">
@@ -57977,12 +58060,8 @@
       <c r="Q1178" s="4"/>
       <c r="R1178" s="4"/>
       <c r="S1178" s="2"/>
-      <c r="T1178" s="5"/>
-      <c r="U1178" s="5"/>
       <c r="V1178" s="2"/>
       <c r="W1178" s="2"/>
-      <c r="X1178" s="5"/>
-      <c r="Y1178" s="5"/>
       <c r="Z1178" s="2"/>
       <c r="AA1178" s="2"/>
       <c r="AB1178" s="2"/>
@@ -57991,7 +58070,7 @@
       </c>
     </row>
     <row r="1179" spans="1:29">
-      <c r="A1179" s="5">
+      <c r="A1179">
         <v>2004</v>
       </c>
       <c r="B1179" s="3">
@@ -58006,7 +58085,7 @@
       <c r="E1179" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F1179" s="5">
+      <c r="F1179">
         <v>38142</v>
       </c>
       <c r="G1179" s="2" t="s">
@@ -58024,12 +58103,8 @@
       <c r="Q1179" s="4"/>
       <c r="R1179" s="4"/>
       <c r="S1179" s="2"/>
-      <c r="T1179" s="5"/>
-      <c r="U1179" s="5"/>
       <c r="V1179" s="2"/>
       <c r="W1179" s="2"/>
-      <c r="X1179" s="5"/>
-      <c r="Y1179" s="5"/>
       <c r="Z1179" s="2"/>
       <c r="AA1179" s="2"/>
       <c r="AB1179" s="2"/>
@@ -58038,7 +58113,7 @@
       </c>
     </row>
     <row r="1180" spans="1:29">
-      <c r="A1180" s="5">
+      <c r="A1180">
         <v>2005</v>
       </c>
       <c r="B1180" s="3">
@@ -58053,7 +58128,7 @@
       <c r="E1180" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F1180" s="5">
+      <c r="F1180">
         <v>38567</v>
       </c>
       <c r="G1180" s="2" t="s">
@@ -58071,12 +58146,8 @@
       <c r="Q1180" s="4"/>
       <c r="R1180" s="4"/>
       <c r="S1180" s="2"/>
-      <c r="T1180" s="5"/>
-      <c r="U1180" s="5"/>
       <c r="V1180" s="2"/>
       <c r="W1180" s="2"/>
-      <c r="X1180" s="5"/>
-      <c r="Y1180" s="5"/>
       <c r="Z1180" s="2"/>
       <c r="AA1180" s="2" t="s">
         <v>1782</v>
@@ -58087,7 +58158,7 @@
       <c r="AC1180" s="2"/>
     </row>
     <row r="1181" spans="1:29">
-      <c r="A1181" s="5">
+      <c r="A1181">
         <v>2006</v>
       </c>
       <c r="B1181" s="3">
@@ -58102,7 +58173,7 @@
       <c r="E1181" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F1181" s="5">
+      <c r="F1181">
         <v>38567</v>
       </c>
       <c r="G1181" s="2" t="s">
@@ -58120,12 +58191,8 @@
       <c r="Q1181" s="4"/>
       <c r="R1181" s="4"/>
       <c r="S1181" s="2"/>
-      <c r="T1181" s="5"/>
-      <c r="U1181" s="5"/>
       <c r="V1181" s="2"/>
       <c r="W1181" s="2"/>
-      <c r="X1181" s="5"/>
-      <c r="Y1181" s="5"/>
       <c r="Z1181" s="2"/>
       <c r="AA1181" s="2"/>
       <c r="AB1181" s="2"/>
@@ -58134,7 +58201,7 @@
       </c>
     </row>
     <row r="1182" spans="1:29">
-      <c r="A1182" s="5">
+      <c r="A1182">
         <v>2007</v>
       </c>
       <c r="B1182" s="3">
@@ -58149,7 +58216,7 @@
       <c r="E1182" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F1182" s="5">
+      <c r="F1182">
         <v>38351</v>
       </c>
       <c r="G1182" s="2" t="s">
@@ -58167,12 +58234,8 @@
       <c r="Q1182" s="4"/>
       <c r="R1182" s="4"/>
       <c r="S1182" s="2"/>
-      <c r="T1182" s="5"/>
-      <c r="U1182" s="5"/>
       <c r="V1182" s="2"/>
       <c r="W1182" s="2"/>
-      <c r="X1182" s="5"/>
-      <c r="Y1182" s="5"/>
       <c r="Z1182" s="2"/>
       <c r="AA1182" s="2" t="s">
         <v>1785</v>
@@ -58183,7 +58246,7 @@
       <c r="AC1182" s="2"/>
     </row>
     <row r="1183" spans="1:29">
-      <c r="A1183" s="5">
+      <c r="A1183">
         <v>2008</v>
       </c>
       <c r="B1183" s="3">
@@ -58198,7 +58261,7 @@
       <c r="E1183" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F1183" s="5">
+      <c r="F1183">
         <v>38339</v>
       </c>
       <c r="G1183" s="2" t="s">
@@ -58216,12 +58279,8 @@
       <c r="Q1183" s="4"/>
       <c r="R1183" s="4"/>
       <c r="S1183" s="2"/>
-      <c r="T1183" s="5"/>
-      <c r="U1183" s="5"/>
       <c r="V1183" s="2"/>
       <c r="W1183" s="2"/>
-      <c r="X1183" s="5"/>
-      <c r="Y1183" s="5"/>
       <c r="Z1183" s="2"/>
       <c r="AA1183" s="2"/>
       <c r="AB1183" s="2"/>
@@ -58230,7 +58289,7 @@
       </c>
     </row>
     <row r="1184" spans="1:29">
-      <c r="A1184" s="5">
+      <c r="A1184">
         <v>2009</v>
       </c>
       <c r="B1184" s="3">
@@ -58245,7 +58304,7 @@
       <c r="E1184" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F1184" s="5">
+      <c r="F1184">
         <v>38351</v>
       </c>
       <c r="G1184" s="2" t="s">
@@ -58263,12 +58322,8 @@
       <c r="Q1184" s="4"/>
       <c r="R1184" s="4"/>
       <c r="S1184" s="2"/>
-      <c r="T1184" s="5"/>
-      <c r="U1184" s="5"/>
       <c r="V1184" s="2"/>
       <c r="W1184" s="2"/>
-      <c r="X1184" s="5"/>
-      <c r="Y1184" s="5"/>
       <c r="Z1184" s="2"/>
       <c r="AA1184" s="2"/>
       <c r="AB1184" s="2"/>
@@ -58277,7 +58332,7 @@
       </c>
     </row>
     <row r="1185" spans="1:29">
-      <c r="A1185" s="5">
+      <c r="A1185">
         <v>2010</v>
       </c>
       <c r="B1185" s="3">
@@ -58292,7 +58347,7 @@
       <c r="E1185" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="F1185" s="5">
+      <c r="F1185">
         <v>43195</v>
       </c>
       <c r="G1185" s="2" t="s">
@@ -58310,12 +58365,8 @@
       <c r="Q1185" s="4"/>
       <c r="R1185" s="4"/>
       <c r="S1185" s="2"/>
-      <c r="T1185" s="5"/>
-      <c r="U1185" s="5"/>
       <c r="V1185" s="2"/>
       <c r="W1185" s="2"/>
-      <c r="X1185" s="5"/>
-      <c r="Y1185" s="5"/>
       <c r="Z1185" s="2"/>
       <c r="AA1185" s="2"/>
       <c r="AB1185" s="2"/>
@@ -58324,7 +58375,7 @@
       </c>
     </row>
     <row r="1186" spans="1:29">
-      <c r="A1186" s="5">
+      <c r="A1186">
         <v>2011</v>
       </c>
       <c r="B1186" s="3">
@@ -58339,7 +58390,7 @@
       <c r="E1186" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F1186" s="5">
+      <c r="F1186">
         <v>43164</v>
       </c>
       <c r="G1186" s="2" t="s">
@@ -58357,12 +58408,8 @@
       <c r="Q1186" s="4"/>
       <c r="R1186" s="4"/>
       <c r="S1186" s="2"/>
-      <c r="T1186" s="5"/>
-      <c r="U1186" s="5"/>
       <c r="V1186" s="2"/>
       <c r="W1186" s="2"/>
-      <c r="X1186" s="5"/>
-      <c r="Y1186" s="5"/>
       <c r="Z1186" s="2"/>
       <c r="AA1186" s="2"/>
       <c r="AB1186" s="2"/>
@@ -58371,7 +58418,7 @@
       </c>
     </row>
     <row r="1187" spans="1:29">
-      <c r="A1187" s="5">
+      <c r="A1187">
         <v>2012</v>
       </c>
       <c r="B1187" s="3">
@@ -58386,7 +58433,7 @@
       <c r="E1187" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F1187" s="5">
+      <c r="F1187">
         <v>43130</v>
       </c>
       <c r="G1187" s="2" t="s">
@@ -58404,12 +58451,8 @@
       <c r="Q1187" s="4"/>
       <c r="R1187" s="4"/>
       <c r="S1187" s="2"/>
-      <c r="T1187" s="5"/>
-      <c r="U1187" s="5"/>
       <c r="V1187" s="2"/>
       <c r="W1187" s="2"/>
-      <c r="X1187" s="5"/>
-      <c r="Y1187" s="5"/>
       <c r="Z1187" s="2"/>
       <c r="AA1187" s="2"/>
       <c r="AB1187" s="2"/>
@@ -58418,7 +58461,7 @@
       </c>
     </row>
     <row r="1188" spans="1:29">
-      <c r="A1188" s="5">
+      <c r="A1188">
         <v>2013</v>
       </c>
       <c r="B1188" s="3">
@@ -58433,7 +58476,7 @@
       <c r="E1188" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="F1188" s="5">
+      <c r="F1188">
         <v>38532</v>
       </c>
       <c r="G1188" s="2" t="s">
@@ -58451,12 +58494,8 @@
       <c r="Q1188" s="4"/>
       <c r="R1188" s="4"/>
       <c r="S1188" s="2"/>
-      <c r="T1188" s="5"/>
-      <c r="U1188" s="5"/>
       <c r="V1188" s="2"/>
       <c r="W1188" s="2"/>
-      <c r="X1188" s="5"/>
-      <c r="Y1188" s="5"/>
       <c r="Z1188" s="2"/>
       <c r="AA1188" s="2"/>
       <c r="AB1188" s="2"/>
@@ -58465,7 +58504,7 @@
       </c>
     </row>
     <row r="1189" spans="1:29">
-      <c r="A1189" s="5">
+      <c r="A1189">
         <v>2014</v>
       </c>
       <c r="B1189" s="3">
@@ -58480,7 +58519,7 @@
       <c r="E1189" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F1189" s="5">
+      <c r="F1189">
         <v>38166</v>
       </c>
       <c r="G1189" s="2" t="s">
@@ -58498,12 +58537,8 @@
       <c r="Q1189" s="4"/>
       <c r="R1189" s="4"/>
       <c r="S1189" s="2"/>
-      <c r="T1189" s="5"/>
-      <c r="U1189" s="5"/>
       <c r="V1189" s="2"/>
       <c r="W1189" s="2"/>
-      <c r="X1189" s="5"/>
-      <c r="Y1189" s="5"/>
       <c r="Z1189" s="2"/>
       <c r="AA1189" s="2"/>
       <c r="AB1189" s="2"/>
@@ -58512,7 +58547,7 @@
       </c>
     </row>
     <row r="1190" spans="1:29">
-      <c r="A1190" s="5">
+      <c r="A1190">
         <v>2015</v>
       </c>
       <c r="B1190" s="3">
@@ -58527,7 +58562,7 @@
       <c r="E1190" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F1190" s="5">
+      <c r="F1190">
         <v>38511</v>
       </c>
       <c r="G1190" s="2" t="s">
@@ -58545,12 +58580,8 @@
       <c r="Q1190" s="4"/>
       <c r="R1190" s="4"/>
       <c r="S1190" s="2"/>
-      <c r="T1190" s="5"/>
-      <c r="U1190" s="5"/>
       <c r="V1190" s="2"/>
       <c r="W1190" s="2"/>
-      <c r="X1190" s="5"/>
-      <c r="Y1190" s="5"/>
       <c r="Z1190" s="2"/>
       <c r="AA1190" s="2"/>
       <c r="AB1190" s="2"/>
@@ -58559,7 +58590,7 @@
       </c>
     </row>
     <row r="1191" spans="1:29">
-      <c r="A1191" s="5">
+      <c r="A1191">
         <v>2016</v>
       </c>
       <c r="B1191" s="3">
@@ -58574,7 +58605,7 @@
       <c r="E1191" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="F1191" s="5">
+      <c r="F1191">
         <v>38158</v>
       </c>
       <c r="G1191" s="2" t="s">
@@ -58594,19 +58625,15 @@
       <c r="Q1191" s="4"/>
       <c r="R1191" s="4"/>
       <c r="S1191" s="2"/>
-      <c r="T1191" s="5"/>
-      <c r="U1191" s="5"/>
       <c r="V1191" s="2"/>
       <c r="W1191" s="2"/>
-      <c r="X1191" s="5"/>
-      <c r="Y1191" s="5"/>
       <c r="Z1191" s="2"/>
       <c r="AA1191" s="2"/>
       <c r="AB1191" s="2"/>
       <c r="AC1191" s="2"/>
     </row>
     <row r="1192" spans="1:29">
-      <c r="A1192" s="5">
+      <c r="A1192">
         <v>2017</v>
       </c>
       <c r="B1192" s="3">
@@ -58621,7 +58648,7 @@
       <c r="E1192" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="F1192" s="5">
+      <c r="F1192">
         <v>38810</v>
       </c>
       <c r="G1192" s="2" t="s">
@@ -58639,12 +58666,8 @@
       <c r="Q1192" s="4"/>
       <c r="R1192" s="4"/>
       <c r="S1192" s="2"/>
-      <c r="T1192" s="5"/>
-      <c r="U1192" s="5"/>
       <c r="V1192" s="2"/>
       <c r="W1192" s="2"/>
-      <c r="X1192" s="5"/>
-      <c r="Y1192" s="5"/>
       <c r="Z1192" s="2"/>
       <c r="AA1192" s="2"/>
       <c r="AB1192" s="2"/>
@@ -58653,7 +58676,7 @@
       </c>
     </row>
     <row r="1193" spans="1:29">
-      <c r="A1193" s="5">
+      <c r="A1193">
         <v>2018</v>
       </c>
       <c r="B1193" s="3">
@@ -58668,7 +58691,7 @@
       <c r="E1193" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="F1193" s="5">
+      <c r="F1193">
         <v>43194</v>
       </c>
       <c r="G1193" s="2" t="s">
@@ -58686,12 +58709,8 @@
       <c r="Q1193" s="4"/>
       <c r="R1193" s="4"/>
       <c r="S1193" s="2"/>
-      <c r="T1193" s="5"/>
-      <c r="U1193" s="5"/>
       <c r="V1193" s="2"/>
       <c r="W1193" s="2"/>
-      <c r="X1193" s="5"/>
-      <c r="Y1193" s="5"/>
       <c r="Z1193" s="2"/>
       <c r="AA1193" s="2"/>
       <c r="AB1193" s="2"/>
@@ -58700,7 +58719,7 @@
       </c>
     </row>
     <row r="1194" spans="1:29">
-      <c r="A1194" s="5">
+      <c r="A1194">
         <v>2019</v>
       </c>
       <c r="B1194" s="3">
@@ -58715,7 +58734,7 @@
       <c r="E1194" s="2" t="s">
         <v>1799</v>
       </c>
-      <c r="F1194" s="5">
+      <c r="F1194">
         <v>38142</v>
       </c>
       <c r="G1194" s="2" t="s">
@@ -58735,19 +58754,15 @@
       <c r="Q1194" s="4"/>
       <c r="R1194" s="4"/>
       <c r="S1194" s="2"/>
-      <c r="T1194" s="5"/>
-      <c r="U1194" s="5"/>
       <c r="V1194" s="2"/>
       <c r="W1194" s="2"/>
-      <c r="X1194" s="5"/>
-      <c r="Y1194" s="5"/>
       <c r="Z1194" s="2"/>
       <c r="AA1194" s="2"/>
       <c r="AB1194" s="2"/>
       <c r="AC1194" s="2"/>
     </row>
     <row r="1195" spans="1:29">
-      <c r="A1195" s="5">
+      <c r="A1195">
         <v>2020</v>
       </c>
       <c r="B1195" s="3">
@@ -58762,7 +58777,7 @@
       <c r="E1195" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="F1195" s="5">
+      <c r="F1195">
         <v>38780</v>
       </c>
       <c r="G1195" s="2" t="s">
@@ -58782,19 +58797,15 @@
       <c r="Q1195" s="4"/>
       <c r="R1195" s="4"/>
       <c r="S1195" s="2"/>
-      <c r="T1195" s="5"/>
-      <c r="U1195" s="5"/>
       <c r="V1195" s="2"/>
       <c r="W1195" s="2"/>
-      <c r="X1195" s="5"/>
-      <c r="Y1195" s="5"/>
       <c r="Z1195" s="2"/>
       <c r="AA1195" s="2"/>
       <c r="AB1195" s="2"/>
       <c r="AC1195" s="2"/>
     </row>
     <row r="1196" spans="1:29">
-      <c r="A1196" s="5">
+      <c r="A1196">
         <v>2021</v>
       </c>
       <c r="B1196" s="3">
@@ -58809,7 +58820,7 @@
       <c r="E1196" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F1196" s="5">
+      <c r="F1196">
         <v>38119</v>
       </c>
       <c r="G1196" s="2" t="s">
@@ -58827,12 +58838,8 @@
       <c r="Q1196" s="4"/>
       <c r="R1196" s="4"/>
       <c r="S1196" s="2"/>
-      <c r="T1196" s="5"/>
-      <c r="U1196" s="5"/>
       <c r="V1196" s="2"/>
       <c r="W1196" s="2"/>
-      <c r="X1196" s="5"/>
-      <c r="Y1196" s="5"/>
       <c r="Z1196" s="2"/>
       <c r="AA1196" s="2"/>
       <c r="AB1196" s="2"/>
@@ -58841,7 +58848,7 @@
       </c>
     </row>
     <row r="1197" spans="1:29">
-      <c r="A1197" s="5">
+      <c r="A1197">
         <v>2022</v>
       </c>
       <c r="B1197" s="3">
@@ -58856,7 +58863,7 @@
       <c r="E1197" s="2" t="s">
         <v>1500</v>
       </c>
-      <c r="F1197" s="5">
+      <c r="F1197">
         <v>38553</v>
       </c>
       <c r="G1197" s="2" t="s">
@@ -58876,19 +58883,15 @@
       <c r="Q1197" s="4"/>
       <c r="R1197" s="4"/>
       <c r="S1197" s="2"/>
-      <c r="T1197" s="5"/>
-      <c r="U1197" s="5"/>
       <c r="V1197" s="2"/>
       <c r="W1197" s="2"/>
-      <c r="X1197" s="5"/>
-      <c r="Y1197" s="5"/>
       <c r="Z1197" s="2"/>
       <c r="AA1197" s="2"/>
       <c r="AB1197" s="2"/>
       <c r="AC1197" s="2"/>
     </row>
     <row r="1198" spans="1:29">
-      <c r="A1198" s="5">
+      <c r="A1198">
         <v>2023</v>
       </c>
       <c r="B1198" s="3">
@@ -58903,7 +58906,7 @@
       <c r="E1198" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F1198" s="5">
+      <c r="F1198">
         <v>43183</v>
       </c>
       <c r="G1198" s="2" t="s">
@@ -58921,12 +58924,8 @@
       <c r="Q1198" s="4"/>
       <c r="R1198" s="4"/>
       <c r="S1198" s="2"/>
-      <c r="T1198" s="5"/>
-      <c r="U1198" s="5"/>
       <c r="V1198" s="2"/>
       <c r="W1198" s="2"/>
-      <c r="X1198" s="5"/>
-      <c r="Y1198" s="5"/>
       <c r="Z1198" s="2"/>
       <c r="AA1198" s="2"/>
       <c r="AB1198" s="2"/>
@@ -58935,7 +58934,7 @@
       </c>
     </row>
     <row r="1199" spans="1:29">
-      <c r="A1199" s="5">
+      <c r="A1199">
         <v>2024</v>
       </c>
       <c r="B1199" s="3">
@@ -58950,7 +58949,7 @@
       <c r="E1199" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F1199" s="5">
+      <c r="F1199">
         <v>38411</v>
       </c>
       <c r="G1199" s="2" t="s">
@@ -58968,12 +58967,8 @@
       <c r="Q1199" s="4"/>
       <c r="R1199" s="4"/>
       <c r="S1199" s="2"/>
-      <c r="T1199" s="5"/>
-      <c r="U1199" s="5"/>
       <c r="V1199" s="2"/>
       <c r="W1199" s="2"/>
-      <c r="X1199" s="5"/>
-      <c r="Y1199" s="5"/>
       <c r="Z1199" s="2"/>
       <c r="AA1199" s="2"/>
       <c r="AB1199" s="2"/>
@@ -58982,7 +58977,7 @@
       </c>
     </row>
     <row r="1200" spans="1:29">
-      <c r="A1200" s="5">
+      <c r="A1200">
         <v>2025</v>
       </c>
       <c r="B1200" s="3">
@@ -58997,7 +58992,7 @@
       <c r="E1200" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="F1200" s="5">
+      <c r="F1200">
         <v>38837</v>
       </c>
       <c r="G1200" s="2" t="s">
@@ -59015,12 +59010,8 @@
       <c r="Q1200" s="4"/>
       <c r="R1200" s="4"/>
       <c r="S1200" s="2"/>
-      <c r="T1200" s="5"/>
-      <c r="U1200" s="5"/>
       <c r="V1200" s="2"/>
       <c r="W1200" s="2"/>
-      <c r="X1200" s="5"/>
-      <c r="Y1200" s="5"/>
       <c r="Z1200" s="2"/>
       <c r="AA1200" s="2"/>
       <c r="AB1200" s="2"/>
@@ -59029,7 +59020,7 @@
       </c>
     </row>
     <row r="1201" spans="1:29">
-      <c r="A1201" s="5">
+      <c r="A1201">
         <v>2026</v>
       </c>
       <c r="B1201" s="3">
@@ -59044,7 +59035,7 @@
       <c r="E1201" s="2" t="s">
         <v>1808</v>
       </c>
-      <c r="F1201" s="5">
+      <c r="F1201">
         <v>38996</v>
       </c>
       <c r="G1201" s="2" t="s">
@@ -59062,12 +59053,8 @@
       <c r="Q1201" s="4"/>
       <c r="R1201" s="4"/>
       <c r="S1201" s="2"/>
-      <c r="T1201" s="5"/>
-      <c r="U1201" s="5"/>
       <c r="V1201" s="2"/>
       <c r="W1201" s="2"/>
-      <c r="X1201" s="5"/>
-      <c r="Y1201" s="5"/>
       <c r="Z1201" s="2"/>
       <c r="AA1201" s="2"/>
       <c r="AB1201" s="2"/>
@@ -59076,7 +59063,7 @@
       </c>
     </row>
     <row r="1202" spans="1:29">
-      <c r="A1202" s="5">
+      <c r="A1202">
         <v>2027</v>
       </c>
       <c r="B1202" s="3">
@@ -59091,7 +59078,7 @@
       <c r="E1202" s="2" t="s">
         <v>1500</v>
       </c>
-      <c r="F1202" s="5">
+      <c r="F1202">
         <v>38466</v>
       </c>
       <c r="G1202" s="2" t="s">
@@ -59111,19 +59098,15 @@
       <c r="Q1202" s="4"/>
       <c r="R1202" s="4"/>
       <c r="S1202" s="2"/>
-      <c r="T1202" s="5"/>
-      <c r="U1202" s="5"/>
       <c r="V1202" s="2"/>
       <c r="W1202" s="2"/>
-      <c r="X1202" s="5"/>
-      <c r="Y1202" s="5"/>
       <c r="Z1202" s="2"/>
       <c r="AA1202" s="2"/>
       <c r="AB1202" s="2"/>
       <c r="AC1202" s="2"/>
     </row>
     <row r="1203" spans="1:29">
-      <c r="A1203" s="5">
+      <c r="A1203">
         <v>2028</v>
       </c>
       <c r="B1203" s="3">
@@ -59138,7 +59121,7 @@
       <c r="E1203" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="F1203" s="5">
+      <c r="F1203">
         <v>38532</v>
       </c>
       <c r="G1203" s="2" t="s">
@@ -59158,16 +59141,1060 @@
       <c r="Q1203" s="4"/>
       <c r="R1203" s="4"/>
       <c r="S1203" s="2"/>
-      <c r="T1203" s="5"/>
-      <c r="U1203" s="5"/>
       <c r="V1203" s="2"/>
       <c r="W1203" s="2"/>
-      <c r="X1203" s="5"/>
-      <c r="Y1203" s="5"/>
       <c r="Z1203" s="2"/>
       <c r="AA1203" s="2"/>
       <c r="AB1203" s="2"/>
       <c r="AC1203" s="2"/>
+    </row>
+    <row r="1204" spans="1:29">
+      <c r="A1204" s="5">
+        <v>2029</v>
+      </c>
+      <c r="B1204" s="3">
+        <v>46304.698159722197</v>
+      </c>
+      <c r="C1204" s="3">
+        <v>46304.700775463003</v>
+      </c>
+      <c r="D1204" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="E1204" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="F1204" s="5">
+        <v>38815</v>
+      </c>
+      <c r="G1204" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="H1204" s="2"/>
+      <c r="I1204" s="2"/>
+      <c r="J1204" s="2"/>
+      <c r="K1204" s="2"/>
+      <c r="L1204" s="2"/>
+      <c r="M1204" s="2"/>
+      <c r="N1204" s="2"/>
+      <c r="O1204" s="2"/>
+      <c r="P1204" s="2"/>
+      <c r="Q1204" s="4"/>
+      <c r="R1204" s="4"/>
+      <c r="S1204" s="2"/>
+      <c r="T1204" s="5"/>
+      <c r="U1204" s="5"/>
+      <c r="V1204" s="2"/>
+      <c r="W1204" s="2"/>
+      <c r="X1204" s="5"/>
+      <c r="Y1204" s="5"/>
+      <c r="Z1204" s="2"/>
+      <c r="AA1204" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AB1204" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AC1204" s="2"/>
+    </row>
+    <row r="1205" spans="1:29">
+      <c r="A1205" s="5">
+        <v>2030</v>
+      </c>
+      <c r="B1205" s="3">
+        <v>46304.713668981502</v>
+      </c>
+      <c r="C1205" s="3">
+        <v>46304.714166666701</v>
+      </c>
+      <c r="D1205" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E1205" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="F1205" s="5">
+        <v>38363</v>
+      </c>
+      <c r="G1205" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1205" s="2"/>
+      <c r="I1205" s="2"/>
+      <c r="J1205" s="2"/>
+      <c r="K1205" s="2"/>
+      <c r="L1205" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="M1205" s="2"/>
+      <c r="N1205" s="2"/>
+      <c r="O1205" s="2"/>
+      <c r="P1205" s="2"/>
+      <c r="Q1205" s="4"/>
+      <c r="R1205" s="4"/>
+      <c r="S1205" s="2"/>
+      <c r="T1205" s="5"/>
+      <c r="U1205" s="5"/>
+      <c r="V1205" s="2"/>
+      <c r="W1205" s="2"/>
+      <c r="X1205" s="5"/>
+      <c r="Y1205" s="5"/>
+      <c r="Z1205" s="2"/>
+      <c r="AA1205" s="2"/>
+      <c r="AB1205" s="2"/>
+      <c r="AC1205" s="2"/>
+    </row>
+    <row r="1206" spans="1:29">
+      <c r="A1206" s="5">
+        <v>2031</v>
+      </c>
+      <c r="B1206" s="3">
+        <v>46304.722222222197</v>
+      </c>
+      <c r="C1206" s="3">
+        <v>46304.722962963002</v>
+      </c>
+      <c r="D1206" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1206" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1206" s="5">
+        <v>38535</v>
+      </c>
+      <c r="G1206" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1206" s="2"/>
+      <c r="I1206" s="2"/>
+      <c r="J1206" s="2"/>
+      <c r="K1206" s="2"/>
+      <c r="L1206" s="2"/>
+      <c r="M1206" s="2"/>
+      <c r="N1206" s="2"/>
+      <c r="O1206" s="2"/>
+      <c r="P1206" s="2"/>
+      <c r="Q1206" s="4"/>
+      <c r="R1206" s="4"/>
+      <c r="S1206" s="2"/>
+      <c r="T1206" s="5"/>
+      <c r="U1206" s="5"/>
+      <c r="V1206" s="2"/>
+      <c r="W1206" s="2"/>
+      <c r="X1206" s="5"/>
+      <c r="Y1206" s="5"/>
+      <c r="Z1206" s="2"/>
+      <c r="AA1206" s="2"/>
+      <c r="AB1206" s="2"/>
+      <c r="AC1206" s="2" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:29">
+      <c r="A1207" s="5">
+        <v>2032</v>
+      </c>
+      <c r="B1207" s="3">
+        <v>46304.723715277803</v>
+      </c>
+      <c r="C1207" s="3">
+        <v>46304.724479166704</v>
+      </c>
+      <c r="D1207" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1207" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1207" s="5">
+        <v>38142</v>
+      </c>
+      <c r="G1207" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1207" s="2"/>
+      <c r="I1207" s="2"/>
+      <c r="J1207" s="2"/>
+      <c r="K1207" s="2"/>
+      <c r="L1207" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="M1207" s="2"/>
+      <c r="N1207" s="2"/>
+      <c r="O1207" s="2"/>
+      <c r="P1207" s="2"/>
+      <c r="Q1207" s="4"/>
+      <c r="R1207" s="4"/>
+      <c r="S1207" s="2"/>
+      <c r="T1207" s="5"/>
+      <c r="U1207" s="5"/>
+      <c r="V1207" s="2"/>
+      <c r="W1207" s="2"/>
+      <c r="X1207" s="5"/>
+      <c r="Y1207" s="5"/>
+      <c r="Z1207" s="2"/>
+      <c r="AA1207" s="2"/>
+      <c r="AB1207" s="2"/>
+      <c r="AC1207" s="2"/>
+    </row>
+    <row r="1208" spans="1:29">
+      <c r="A1208" s="5">
+        <v>2033</v>
+      </c>
+      <c r="B1208" s="3">
+        <v>46304.729178240697</v>
+      </c>
+      <c r="C1208" s="3">
+        <v>46304.729629629597</v>
+      </c>
+      <c r="D1208" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E1208" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="F1208" s="5">
+        <v>43162</v>
+      </c>
+      <c r="G1208" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1208" s="2"/>
+      <c r="I1208" s="2"/>
+      <c r="J1208" s="2"/>
+      <c r="K1208" s="2"/>
+      <c r="L1208" s="2"/>
+      <c r="M1208" s="2"/>
+      <c r="N1208" s="2"/>
+      <c r="O1208" s="2"/>
+      <c r="P1208" s="2"/>
+      <c r="Q1208" s="4"/>
+      <c r="R1208" s="4"/>
+      <c r="S1208" s="2"/>
+      <c r="T1208" s="5"/>
+      <c r="U1208" s="5"/>
+      <c r="V1208" s="2"/>
+      <c r="W1208" s="2"/>
+      <c r="X1208" s="5"/>
+      <c r="Y1208" s="5"/>
+      <c r="Z1208" s="2"/>
+      <c r="AA1208" s="2"/>
+      <c r="AB1208" s="2"/>
+      <c r="AC1208" s="2" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:29">
+      <c r="A1209" s="5">
+        <v>2034</v>
+      </c>
+      <c r="B1209" s="3">
+        <v>46304.7351851852</v>
+      </c>
+      <c r="C1209" s="3">
+        <v>46304.736122685201</v>
+      </c>
+      <c r="D1209" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1209" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F1209" s="5">
+        <v>38371</v>
+      </c>
+      <c r="G1209" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1209" s="2"/>
+      <c r="I1209" s="2"/>
+      <c r="J1209" s="2"/>
+      <c r="K1209" s="2"/>
+      <c r="L1209" s="2"/>
+      <c r="M1209" s="2"/>
+      <c r="N1209" s="2"/>
+      <c r="O1209" s="2"/>
+      <c r="P1209" s="2"/>
+      <c r="Q1209" s="4"/>
+      <c r="R1209" s="4"/>
+      <c r="S1209" s="2"/>
+      <c r="T1209" s="5"/>
+      <c r="U1209" s="5"/>
+      <c r="V1209" s="2"/>
+      <c r="W1209" s="2"/>
+      <c r="X1209" s="5"/>
+      <c r="Y1209" s="5"/>
+      <c r="Z1209" s="2"/>
+      <c r="AA1209" s="2"/>
+      <c r="AB1209" s="2"/>
+      <c r="AC1209" s="2" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:29">
+      <c r="A1210" s="5">
+        <v>2035</v>
+      </c>
+      <c r="B1210" s="3">
+        <v>46304.738946759302</v>
+      </c>
+      <c r="C1210" s="3">
+        <v>46304.739525463003</v>
+      </c>
+      <c r="D1210" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1210" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1210" s="5">
+        <v>38719</v>
+      </c>
+      <c r="G1210" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1210" s="2"/>
+      <c r="I1210" s="2"/>
+      <c r="J1210" s="2"/>
+      <c r="K1210" s="2"/>
+      <c r="L1210" s="2"/>
+      <c r="M1210" s="2"/>
+      <c r="N1210" s="2"/>
+      <c r="O1210" s="2"/>
+      <c r="P1210" s="2"/>
+      <c r="Q1210" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="R1210" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="S1210" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="T1210" s="5"/>
+      <c r="U1210" s="5"/>
+      <c r="V1210" s="2"/>
+      <c r="W1210" s="2"/>
+      <c r="X1210" s="5"/>
+      <c r="Y1210" s="5"/>
+      <c r="Z1210" s="2"/>
+      <c r="AA1210" s="2"/>
+      <c r="AB1210" s="2"/>
+      <c r="AC1210" s="2"/>
+    </row>
+    <row r="1211" spans="1:29">
+      <c r="A1211" s="5">
+        <v>2036</v>
+      </c>
+      <c r="B1211" s="3">
+        <v>46304.739699074104</v>
+      </c>
+      <c r="C1211" s="3">
+        <v>46304.7429513889</v>
+      </c>
+      <c r="D1211" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1211" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1211" s="5">
+        <v>38719</v>
+      </c>
+      <c r="G1211" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1211" s="2"/>
+      <c r="I1211" s="2"/>
+      <c r="J1211" s="2"/>
+      <c r="K1211" s="2"/>
+      <c r="L1211" s="2"/>
+      <c r="M1211" s="2"/>
+      <c r="N1211" s="2"/>
+      <c r="O1211" s="2"/>
+      <c r="P1211" s="2"/>
+      <c r="Q1211" s="4"/>
+      <c r="R1211" s="4"/>
+      <c r="S1211" s="2"/>
+      <c r="T1211" s="5"/>
+      <c r="U1211" s="5"/>
+      <c r="V1211" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="W1211" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="X1211" s="5"/>
+      <c r="Y1211" s="5"/>
+      <c r="Z1211" s="2"/>
+      <c r="AA1211" s="2"/>
+      <c r="AB1211" s="2"/>
+      <c r="AC1211" s="2"/>
+    </row>
+    <row r="1212" spans="1:29">
+      <c r="A1212" s="5">
+        <v>2037</v>
+      </c>
+      <c r="B1212" s="3">
+        <v>46304.748773148203</v>
+      </c>
+      <c r="C1212" s="3">
+        <v>46304.754236111097</v>
+      </c>
+      <c r="D1212" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E1212" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="F1212" s="5">
+        <v>39179</v>
+      </c>
+      <c r="G1212" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="H1212" s="2"/>
+      <c r="I1212" s="2"/>
+      <c r="J1212" s="2"/>
+      <c r="K1212" s="2"/>
+      <c r="L1212" s="2"/>
+      <c r="M1212" s="2"/>
+      <c r="N1212" s="2"/>
+      <c r="O1212" s="2"/>
+      <c r="P1212" s="2"/>
+      <c r="Q1212" s="4"/>
+      <c r="R1212" s="4"/>
+      <c r="S1212" s="2"/>
+      <c r="T1212" s="5"/>
+      <c r="U1212" s="5"/>
+      <c r="V1212" s="2"/>
+      <c r="W1212" s="2"/>
+      <c r="X1212" s="5"/>
+      <c r="Y1212" s="5"/>
+      <c r="Z1212" s="2"/>
+      <c r="AA1212" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="AB1212" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AC1212" s="2"/>
+    </row>
+    <row r="1213" spans="1:29">
+      <c r="A1213" s="5">
+        <v>2038</v>
+      </c>
+      <c r="B1213" s="3">
+        <v>46304.760879629597</v>
+      </c>
+      <c r="C1213" s="3">
+        <v>46304.761099536998</v>
+      </c>
+      <c r="D1213" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E1213" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F1213" s="5">
+        <v>38633</v>
+      </c>
+      <c r="G1213" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1213" s="2"/>
+      <c r="I1213" s="2"/>
+      <c r="J1213" s="2"/>
+      <c r="K1213" s="2"/>
+      <c r="L1213" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="M1213" s="2"/>
+      <c r="N1213" s="2"/>
+      <c r="O1213" s="2"/>
+      <c r="P1213" s="2"/>
+      <c r="Q1213" s="4"/>
+      <c r="R1213" s="4"/>
+      <c r="S1213" s="2"/>
+      <c r="T1213" s="5"/>
+      <c r="U1213" s="5"/>
+      <c r="V1213" s="2"/>
+      <c r="W1213" s="2"/>
+      <c r="X1213" s="5"/>
+      <c r="Y1213" s="5"/>
+      <c r="Z1213" s="2"/>
+      <c r="AA1213" s="2"/>
+      <c r="AB1213" s="2"/>
+      <c r="AC1213" s="2"/>
+    </row>
+    <row r="1214" spans="1:29">
+      <c r="A1214" s="5">
+        <v>2039</v>
+      </c>
+      <c r="B1214" s="3">
+        <v>46304.765208333301</v>
+      </c>
+      <c r="C1214" s="3">
+        <v>46304.767685185201</v>
+      </c>
+      <c r="D1214" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E1214" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F1214" s="5">
+        <v>38801</v>
+      </c>
+      <c r="G1214" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1214" s="2"/>
+      <c r="I1214" s="2"/>
+      <c r="J1214" s="2"/>
+      <c r="K1214" s="2"/>
+      <c r="L1214" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="M1214" s="2"/>
+      <c r="N1214" s="2"/>
+      <c r="O1214" s="2"/>
+      <c r="P1214" s="2"/>
+      <c r="Q1214" s="4"/>
+      <c r="R1214" s="4"/>
+      <c r="S1214" s="2"/>
+      <c r="T1214" s="5"/>
+      <c r="U1214" s="5"/>
+      <c r="V1214" s="2"/>
+      <c r="W1214" s="2"/>
+      <c r="X1214" s="5"/>
+      <c r="Y1214" s="5"/>
+      <c r="Z1214" s="2"/>
+      <c r="AA1214" s="2"/>
+      <c r="AB1214" s="2"/>
+      <c r="AC1214" s="2"/>
+    </row>
+    <row r="1215" spans="1:29">
+      <c r="A1215" s="5">
+        <v>2040</v>
+      </c>
+      <c r="B1215" s="3">
+        <v>46304.767824074101</v>
+      </c>
+      <c r="C1215" s="3">
+        <v>46304.769895833299</v>
+      </c>
+      <c r="D1215" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E1215" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F1215" s="5">
+        <v>38801</v>
+      </c>
+      <c r="G1215" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="H1215" s="2"/>
+      <c r="I1215" s="2"/>
+      <c r="J1215" s="2"/>
+      <c r="K1215" s="2"/>
+      <c r="L1215" s="2"/>
+      <c r="M1215" s="2"/>
+      <c r="N1215" s="2"/>
+      <c r="O1215" s="2"/>
+      <c r="P1215" s="2"/>
+      <c r="Q1215" s="4"/>
+      <c r="R1215" s="4"/>
+      <c r="S1215" s="2"/>
+      <c r="T1215" s="5">
+        <v>14</v>
+      </c>
+      <c r="U1215" s="5">
+        <v>1</v>
+      </c>
+      <c r="V1215" s="2"/>
+      <c r="W1215" s="2"/>
+      <c r="X1215" s="5"/>
+      <c r="Y1215" s="5"/>
+      <c r="Z1215" s="2"/>
+      <c r="AA1215" s="2"/>
+      <c r="AB1215" s="2"/>
+      <c r="AC1215" s="2"/>
+    </row>
+    <row r="1216" spans="1:29">
+      <c r="A1216" s="5">
+        <v>2041</v>
+      </c>
+      <c r="B1216" s="3">
+        <v>46304.770092592596</v>
+      </c>
+      <c r="C1216" s="3">
+        <v>46304.771990740701</v>
+      </c>
+      <c r="D1216" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E1216" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F1216" s="5">
+        <v>38546</v>
+      </c>
+      <c r="G1216" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1216" s="2"/>
+      <c r="I1216" s="2"/>
+      <c r="J1216" s="2"/>
+      <c r="K1216" s="2"/>
+      <c r="L1216" s="2"/>
+      <c r="M1216" s="2"/>
+      <c r="N1216" s="2"/>
+      <c r="O1216" s="2"/>
+      <c r="P1216" s="2"/>
+      <c r="Q1216" s="4"/>
+      <c r="R1216" s="4"/>
+      <c r="S1216" s="2"/>
+      <c r="T1216" s="5"/>
+      <c r="U1216" s="5"/>
+      <c r="V1216" s="2"/>
+      <c r="W1216" s="2"/>
+      <c r="X1216" s="5"/>
+      <c r="Y1216" s="5"/>
+      <c r="Z1216" s="2"/>
+      <c r="AA1216" s="2"/>
+      <c r="AB1216" s="2"/>
+      <c r="AC1216" s="2" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:29">
+      <c r="A1217" s="5">
+        <v>2042</v>
+      </c>
+      <c r="B1217" s="3">
+        <v>46304.781412037002</v>
+      </c>
+      <c r="C1217" s="3">
+        <v>46304.781805555598</v>
+      </c>
+      <c r="D1217" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1217" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1217" s="5">
+        <v>38205</v>
+      </c>
+      <c r="G1217" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1217" s="2"/>
+      <c r="I1217" s="2"/>
+      <c r="J1217" s="2"/>
+      <c r="K1217" s="2"/>
+      <c r="L1217" s="2"/>
+      <c r="M1217" s="2"/>
+      <c r="N1217" s="2"/>
+      <c r="O1217" s="2"/>
+      <c r="P1217" s="2"/>
+      <c r="Q1217" s="4"/>
+      <c r="R1217" s="4"/>
+      <c r="S1217" s="2"/>
+      <c r="T1217" s="5"/>
+      <c r="U1217" s="5"/>
+      <c r="V1217" s="2"/>
+      <c r="W1217" s="2"/>
+      <c r="X1217" s="5"/>
+      <c r="Y1217" s="5"/>
+      <c r="Z1217" s="2"/>
+      <c r="AA1217" s="2"/>
+      <c r="AB1217" s="2"/>
+      <c r="AC1217" s="2" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:29">
+      <c r="A1218" s="5">
+        <v>2043</v>
+      </c>
+      <c r="B1218" s="3">
+        <v>46304.789143518501</v>
+      </c>
+      <c r="C1218" s="3">
+        <v>46304.790844907402</v>
+      </c>
+      <c r="D1218" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E1218" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1218" s="5">
+        <v>38657</v>
+      </c>
+      <c r="G1218" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1218" s="2"/>
+      <c r="I1218" s="2"/>
+      <c r="J1218" s="2"/>
+      <c r="K1218" s="2"/>
+      <c r="L1218" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="M1218" s="2"/>
+      <c r="N1218" s="2"/>
+      <c r="O1218" s="2"/>
+      <c r="P1218" s="2"/>
+      <c r="Q1218" s="4"/>
+      <c r="R1218" s="4"/>
+      <c r="S1218" s="2"/>
+      <c r="T1218" s="5"/>
+      <c r="U1218" s="5"/>
+      <c r="V1218" s="2"/>
+      <c r="W1218" s="2"/>
+      <c r="X1218" s="5"/>
+      <c r="Y1218" s="5"/>
+      <c r="Z1218" s="2"/>
+      <c r="AA1218" s="2"/>
+      <c r="AB1218" s="2"/>
+      <c r="AC1218" s="2"/>
+    </row>
+    <row r="1219" spans="1:29">
+      <c r="A1219" s="5">
+        <v>2044</v>
+      </c>
+      <c r="B1219" s="3">
+        <v>46304.792569444398</v>
+      </c>
+      <c r="C1219" s="3">
+        <v>46304.793703703697</v>
+      </c>
+      <c r="D1219" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1219" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1219" s="5">
+        <v>38186</v>
+      </c>
+      <c r="G1219" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1219" s="2"/>
+      <c r="I1219" s="2"/>
+      <c r="J1219" s="2"/>
+      <c r="K1219" s="2"/>
+      <c r="L1219" s="2"/>
+      <c r="M1219" s="2"/>
+      <c r="N1219" s="2"/>
+      <c r="O1219" s="2"/>
+      <c r="P1219" s="2"/>
+      <c r="Q1219" s="4"/>
+      <c r="R1219" s="4"/>
+      <c r="S1219" s="2"/>
+      <c r="T1219" s="5"/>
+      <c r="U1219" s="5"/>
+      <c r="V1219" s="2"/>
+      <c r="W1219" s="2"/>
+      <c r="X1219" s="5"/>
+      <c r="Y1219" s="5"/>
+      <c r="Z1219" s="2"/>
+      <c r="AA1219" s="2"/>
+      <c r="AB1219" s="2"/>
+      <c r="AC1219" s="2" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:29">
+      <c r="A1220" s="5">
+        <v>2045</v>
+      </c>
+      <c r="B1220" s="3">
+        <v>46304.794062499997</v>
+      </c>
+      <c r="C1220" s="3">
+        <v>46304.795266203699</v>
+      </c>
+      <c r="D1220" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="E1220" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F1220" s="5">
+        <v>43111</v>
+      </c>
+      <c r="G1220" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1220" s="2"/>
+      <c r="I1220" s="2"/>
+      <c r="J1220" s="2"/>
+      <c r="K1220" s="2"/>
+      <c r="L1220" s="2"/>
+      <c r="M1220" s="2"/>
+      <c r="N1220" s="2"/>
+      <c r="O1220" s="2"/>
+      <c r="P1220" s="2"/>
+      <c r="Q1220" s="4"/>
+      <c r="R1220" s="4"/>
+      <c r="S1220" s="2"/>
+      <c r="T1220" s="5"/>
+      <c r="U1220" s="5"/>
+      <c r="V1220" s="2"/>
+      <c r="W1220" s="2"/>
+      <c r="X1220" s="5"/>
+      <c r="Y1220" s="5"/>
+      <c r="Z1220" s="2"/>
+      <c r="AA1220" s="2"/>
+      <c r="AB1220" s="2"/>
+      <c r="AC1220" s="2" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:29">
+      <c r="A1221" s="5">
+        <v>2046</v>
+      </c>
+      <c r="B1221" s="3">
+        <v>46304.805057870399</v>
+      </c>
+      <c r="C1221" s="3">
+        <v>46304.805509259299</v>
+      </c>
+      <c r="D1221" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1221" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1221" s="5">
+        <v>43164</v>
+      </c>
+      <c r="G1221" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="H1221" s="2"/>
+      <c r="I1221" s="2"/>
+      <c r="J1221" s="2"/>
+      <c r="K1221" s="2"/>
+      <c r="L1221" s="2"/>
+      <c r="M1221" s="2"/>
+      <c r="N1221" s="2"/>
+      <c r="O1221" s="2"/>
+      <c r="P1221" s="2"/>
+      <c r="Q1221" s="4"/>
+      <c r="R1221" s="4"/>
+      <c r="S1221" s="2"/>
+      <c r="T1221" s="5"/>
+      <c r="U1221" s="5"/>
+      <c r="V1221" s="2"/>
+      <c r="W1221" s="2"/>
+      <c r="X1221" s="5"/>
+      <c r="Y1221" s="5"/>
+      <c r="Z1221" s="2"/>
+      <c r="AA1221" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="AB1221" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="AC1221" s="2"/>
+    </row>
+    <row r="1222" spans="1:29">
+      <c r="A1222" s="5">
+        <v>2047</v>
+      </c>
+      <c r="B1222" s="3">
+        <v>46304.8062152778</v>
+      </c>
+      <c r="C1222" s="3">
+        <v>46304.807488425897</v>
+      </c>
+      <c r="D1222" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1222" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F1222" s="5">
+        <v>38375</v>
+      </c>
+      <c r="G1222" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1222" s="2"/>
+      <c r="I1222" s="2"/>
+      <c r="J1222" s="2"/>
+      <c r="K1222" s="2"/>
+      <c r="L1222" s="2"/>
+      <c r="M1222" s="2"/>
+      <c r="N1222" s="2"/>
+      <c r="O1222" s="2"/>
+      <c r="P1222" s="2"/>
+      <c r="Q1222" s="4"/>
+      <c r="R1222" s="4"/>
+      <c r="S1222" s="2"/>
+      <c r="T1222" s="5"/>
+      <c r="U1222" s="5"/>
+      <c r="V1222" s="2"/>
+      <c r="W1222" s="2"/>
+      <c r="X1222" s="5"/>
+      <c r="Y1222" s="5"/>
+      <c r="Z1222" s="2"/>
+      <c r="AA1222" s="2"/>
+      <c r="AB1222" s="2"/>
+      <c r="AC1222" s="2" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:29">
+      <c r="A1223" s="5">
+        <v>2048</v>
+      </c>
+      <c r="B1223" s="3">
+        <v>46304.808541666702</v>
+      </c>
+      <c r="C1223" s="3">
+        <v>46304.811030092598</v>
+      </c>
+      <c r="D1223" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1223" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F1223" s="5">
+        <v>38651</v>
+      </c>
+      <c r="G1223" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1223" s="2"/>
+      <c r="I1223" s="2"/>
+      <c r="J1223" s="2"/>
+      <c r="K1223" s="2"/>
+      <c r="L1223" s="2"/>
+      <c r="M1223" s="2"/>
+      <c r="N1223" s="2"/>
+      <c r="O1223" s="2"/>
+      <c r="P1223" s="2"/>
+      <c r="Q1223" s="4"/>
+      <c r="R1223" s="4"/>
+      <c r="S1223" s="2"/>
+      <c r="T1223" s="5"/>
+      <c r="U1223" s="5"/>
+      <c r="V1223" s="2"/>
+      <c r="W1223" s="2"/>
+      <c r="X1223" s="5"/>
+      <c r="Y1223" s="5"/>
+      <c r="Z1223" s="2"/>
+      <c r="AA1223" s="2"/>
+      <c r="AB1223" s="2"/>
+      <c r="AC1223" s="2" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:29">
+      <c r="A1224" s="5">
+        <v>2049</v>
+      </c>
+      <c r="B1224" s="3">
+        <v>46304.816724536999</v>
+      </c>
+      <c r="C1224" s="3">
+        <v>46304.839872685203</v>
+      </c>
+      <c r="D1224" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1224" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1224" s="5">
+        <v>38136</v>
+      </c>
+      <c r="G1224" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1224" s="2"/>
+      <c r="I1224" s="2"/>
+      <c r="J1224" s="2"/>
+      <c r="K1224" s="2"/>
+      <c r="L1224" s="2"/>
+      <c r="M1224" s="2"/>
+      <c r="N1224" s="2"/>
+      <c r="O1224" s="2"/>
+      <c r="P1224" s="2"/>
+      <c r="Q1224" s="4"/>
+      <c r="R1224" s="4"/>
+      <c r="S1224" s="2"/>
+      <c r="T1224" s="5"/>
+      <c r="U1224" s="5"/>
+      <c r="V1224" s="2"/>
+      <c r="W1224" s="2"/>
+      <c r="X1224" s="5"/>
+      <c r="Y1224" s="5"/>
+      <c r="Z1224" s="2"/>
+      <c r="AA1224" s="2"/>
+      <c r="AB1224" s="2"/>
+      <c r="AC1224" s="2" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:29">
+      <c r="A1225" s="5">
+        <v>2050</v>
+      </c>
+      <c r="B1225" s="3">
+        <v>46304.857268518499</v>
+      </c>
+      <c r="C1225" s="3">
+        <v>46304.858854166698</v>
+      </c>
+      <c r="D1225" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="E1225" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="F1225" s="5">
+        <v>38568</v>
+      </c>
+      <c r="G1225" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1225" s="2"/>
+      <c r="I1225" s="2"/>
+      <c r="J1225" s="2"/>
+      <c r="K1225" s="2"/>
+      <c r="L1225" s="2"/>
+      <c r="M1225" s="2"/>
+      <c r="N1225" s="2"/>
+      <c r="O1225" s="2"/>
+      <c r="P1225" s="2"/>
+      <c r="Q1225" s="4"/>
+      <c r="R1225" s="4"/>
+      <c r="S1225" s="2"/>
+      <c r="T1225" s="5"/>
+      <c r="U1225" s="5"/>
+      <c r="V1225" s="2"/>
+      <c r="W1225" s="2"/>
+      <c r="X1225" s="5"/>
+      <c r="Y1225" s="5"/>
+      <c r="Z1225" s="2"/>
+      <c r="AA1225" s="2"/>
+      <c r="AB1225" s="2"/>
+      <c r="AC1225" s="2" t="s">
+        <v>1840</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
